--- a/data/sites/hr/Recruiting and Onboarding/recruiting-pipeline-and-requisition-tracker.xlsx
+++ b/data/sites/hr/Recruiting and Onboarding/recruiting-pipeline-and-requisition-tracker.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Recruiting Pipeline and Requisition Tracker</t>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,129 +651,2525 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 1 (Executive Summary &amp; Scope) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Requisitions open longer than 60 days are flagged for a sourcing strategy review. Secondary control 1.2: Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Open Reqs</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Avg Days Open</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Pipeline Stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Onsite</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phone Screen</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Offer</t>
+          <t>Phone Screen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Sourcing</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 10 (Cross-Functional Dependencies) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Time-to-fill target is 35 days for individual contributor roles. Secondary control 10.2: Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 11 (Continuous Improvement Roadmap) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Pipeline health is measured by applicants-to-onsite conversion rate. Secondary control 11.2: Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: Stale requisitions with no activity in 14 days are escalated to the recruiting lead. Secondary control 12.2: Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 2 (Architecture &amp; Process Flow) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Time-to-fill target is 35 days for individual contributor roles. Secondary control 2.2: Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 3 (Governance Standards &amp; Controls) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Pipeline health is measured by applicants-to-onsite conversion rate. Secondary control 3.2: Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 4 (Operational KPIs &amp; Benchmarks) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: Stale requisitions with no activity in 14 days are escalated to the recruiting lead. Secondary control 4.2: Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 5 (Roles, Responsibilities &amp; RACI) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Requisitions open longer than 60 days are flagged for a sourcing strategy review. Secondary control 5.2: Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 6 (Standard Operating Procedures) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Time-to-fill target is 35 days for individual contributor roles. Secondary control 6.2: Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 7 (Risk Register &amp; Mitigations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Pipeline health is measured by applicants-to-onsite conversion rate. Secondary control 7.2: Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Pipeline health is measured by applicants-to-onsite conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 8 (Quality Assurance &amp; Audits) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: Stale requisitions with no activity in 14 days are escalated to the recruiting lead. Secondary control 8.2: Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 9 (Exception Handling &amp; Escalations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Requisitions open longer than 60 days are flagged for a sourcing strategy review. Secondary control 9.2: Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open Reqs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Avg Days Open</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Time-to-fill target is 35 days for individual contributor roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/hr/Recruiting and Onboarding/recruiting-pipeline-and-requisition-tracker.xlsx
+++ b/data/sites/hr/Recruiting and Onboarding/recruiting-pipeline-and-requisition-tracker.xlsx
@@ -17,8 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Sign-off" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1046,7 +1045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Recruiting Pipeline and Requisition Tracker - Section 11: Continuous Improvement Roadmap</t>
+          <t>Recruiting Pipeline and Requisition Tracker - Section 11: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1059,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 11 (Continuous Improvement Roadmap) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 11 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -1240,220 +1239,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Recruiting Pipeline and Requisition Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Weekly snapshot of open requisitions, pipeline stage counts, and time-to-fill against target by department. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: Stale requisitions with no activity in 14 days are escalated to the recruiting lead. Secondary control 12.2: Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Open Reqs</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Avg Days Open</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Pipeline Stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Phone Screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Offer</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Stale requisitions with no activity in 14 days are escalated to the recruiting lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Requisitions open longer than 60 days are flagged for a sourcing strategy review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
